--- a/Sedes_a_priorizar_Yanacona_1.xlsx
+++ b/Sedes_a_priorizar_Yanacona_1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,11 +450,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>219022000341</v>
+        <v>219022001061</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA BALCONCRUZ</t>
+          <t>ESCUELA RURAL MIXTA EL POTRERO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>46.46089396551724</v>
+        <v>47.5236600862069</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>219693000361</v>
+        <v>219392000102</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA CRUZ CHIQUITA</t>
+          <t>ESCUELA RURAL MIXTA LOS ROBLES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,72 +492,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN SEBASTíAN</t>
+          <t>EL MORAL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN</t>
+          <t>LA SIERRA</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49.11702043103448</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>219693000612</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ESCUELA RURAL MIXTA BELLA VISTA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ZONA SUR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SAN SEBASTíAN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SAN SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>49.38112224137931</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>219760000100</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>I.E. PUEBLOQUEMADO - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ZONA SUR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RIO BLANCO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SOTARA</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>49.47095767241379</v>
+        <v>53.02481577586207</v>
       </c>
     </row>
   </sheetData>
